--- a/workspaces/yzz100407/test_output/sample_data/店铺面积表.xlsx
+++ b/workspaces/yzz100407/test_output/sample_data/店铺面积表.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>星巴克咖啡</t>
+          <t>新名咖啡</t>
         </is>
       </c>
       <c r="C2" t="n">
